--- a/Assets/Excel/DataSheet.xlsx
+++ b/Assets/Excel/DataSheet.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nosoead\Desktop\carrerton\Assignment\Internship-assignment\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F240CF93-E83A-433C-BCA0-D5EB1887A3E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864916BD-858C-4F87-B0F8-6D970A6CE1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="MonsterData" sheetId="1" r:id="rId1"/>
-    <sheet name="ItemData" sheetId="2" r:id="rId2"/>
+    <sheet name="MonsterList" sheetId="1" r:id="rId1"/>
+    <sheet name="ItemList" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
   <si>
     <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -137,7 +137,108 @@
     <t>M0005</t>
   </si>
   <si>
-    <t>Skeleton</t>
+    <t>Enemy0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enemy2</t>
+  </si>
+  <si>
+    <t>Enemy3</t>
+  </si>
+  <si>
+    <t>Enemy4</t>
+  </si>
+  <si>
+    <t>초록티를 입었습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주황티를 입었습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뼈다귀 입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강해보이는 뼈다귀입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>머리만 있습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쇠스랑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>낫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>약한총</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그냥총</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쏀총</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>땅을 잘 팔것 같다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건초 긁기 좋게 생겼다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>베기 좋아 보인다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지가 낮은 총입니다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지가 중간인 총입니다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지가 높은 총입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포션</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력 50 회복합니다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000, 30000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">10001, 30000 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10002, 20000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -467,12 +568,13 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.25" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -526,25 +628,217 @@
       <c r="B2" t="s">
         <v>28</v>
       </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2">
+        <v>0.1</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+      <c r="G2">
+        <v>0.1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>10</v>
+      </c>
+      <c r="M2">
+        <v>20</v>
+      </c>
+      <c r="N2" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>24</v>
       </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>0.1</v>
+      </c>
+      <c r="F3">
+        <v>110</v>
+      </c>
+      <c r="G3">
+        <v>0.1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>11</v>
+      </c>
+      <c r="M3">
+        <v>22</v>
+      </c>
+      <c r="N3" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>25</v>
       </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4">
+        <v>14</v>
+      </c>
+      <c r="E4">
+        <v>0.15</v>
+      </c>
+      <c r="F4">
+        <v>120</v>
+      </c>
+      <c r="G4">
+        <v>0.15</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>12</v>
+      </c>
+      <c r="M4">
+        <v>24</v>
+      </c>
+      <c r="N4" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>26</v>
       </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5">
+        <v>16</v>
+      </c>
+      <c r="E5">
+        <v>0.15</v>
+      </c>
+      <c r="F5">
+        <v>150</v>
+      </c>
+      <c r="G5">
+        <v>0.15</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>13</v>
+      </c>
+      <c r="M5">
+        <v>26</v>
+      </c>
+      <c r="N5">
+        <v>20001</v>
+      </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6">
+        <v>18</v>
+      </c>
+      <c r="E6">
+        <v>0.2</v>
+      </c>
+      <c r="F6">
+        <v>200</v>
+      </c>
+      <c r="G6">
+        <v>0.2</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>0.5</v>
+      </c>
+      <c r="L6">
+        <v>14</v>
+      </c>
+      <c r="M6">
+        <v>28</v>
+      </c>
+      <c r="N6">
+        <v>20002</v>
       </c>
     </row>
   </sheetData>
@@ -555,10 +849,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB5EA09-5F15-4CD5-9B49-6E861D044373}">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
@@ -607,6 +901,293 @@
         <v>12</v>
       </c>
     </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>10000</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>10</v>
+      </c>
+      <c r="J2">
+        <v>0.5</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>10001</v>
+      </c>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>20</v>
+      </c>
+      <c r="J3">
+        <v>0.5</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>10002</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>0.5</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>20000</v>
+      </c>
+      <c r="B5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>15</v>
+      </c>
+      <c r="J5">
+        <v>0.4</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>20001</v>
+      </c>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>0.6</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>20002</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>45</v>
+      </c>
+      <c r="J7">
+        <v>0.8</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>30000</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Excel/DataSheet.xlsx
+++ b/Assets/Excel/DataSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nosoead\Desktop\carrerton\Assignment\Internship-assignment\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864916BD-858C-4F87-B0F8-6D970A6CE1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3544696D-AAF4-4CA3-A837-CE357A654947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39270" yWindow="5205" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MonsterList" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
   <si>
     <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -227,18 +227,6 @@
   </si>
   <si>
     <t>체력 50 회복합니다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000, 30000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">10001, 30000 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10002, 20000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -661,8 +649,8 @@
       <c r="M2">
         <v>20</v>
       </c>
-      <c r="N2" t="s">
-        <v>52</v>
+      <c r="N2">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -705,8 +693,8 @@
       <c r="M3">
         <v>22</v>
       </c>
-      <c r="N3" t="s">
-        <v>53</v>
+      <c r="N3">
+        <v>10000</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -749,8 +737,8 @@
       <c r="M4">
         <v>24</v>
       </c>
-      <c r="N4" t="s">
-        <v>54</v>
+      <c r="N4">
+        <v>10001</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -794,7 +782,7 @@
         <v>26</v>
       </c>
       <c r="N5">
-        <v>20001</v>
+        <v>10002</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -838,7 +826,7 @@
         <v>28</v>
       </c>
       <c r="N6">
-        <v>20002</v>
+        <v>30000</v>
       </c>
     </row>
   </sheetData>
